--- a/SGC-CKN/Excel/eaf8162c-45e5-48d7-8fdd-6122755b3d57_CT-02_P14-8_D800_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/eaf8162c-45e5-48d7-8fdd-6122755b3d57_CT-02_P14-8_D800_05-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
   <si>
     <t>Dự án</t>
   </si>
@@ -102,21 +102,17 @@
 05/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">07:20
-05/04/2026</t>
-  </si>
-  <si>
-    <t>Lớp đệm/casing</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">07:30
 05/04/2026</t>
+  </si>
+  <si>
+    <t>Lớp đệm/casing</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">08:00
@@ -345,7 +341,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -355,12 +351,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -516,17 +512,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1165,19 +1161,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="H11" s="5">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J11" s="8">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1194,13 +1190,13 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>34</v>
-      </c>
       <c r="F12" s="9">
-        <v>-1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="G12" s="9">
         <v>-13.2</v>
@@ -1209,65 +1205,65 @@
         <v>0.5</v>
       </c>
       <c r="I12" s="9">
-        <v>12</v>
-      </c>
-      <c r="J12" s="12">
-        <v>24</v>
+        <v>9.4</v>
+      </c>
+      <c r="J12" s="8">
+        <v>18.8</v>
       </c>
       <c r="K12" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="B13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="D13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="15" t="s">
+      <c r="F13" s="12">
+        <v>-13.2</v>
+      </c>
+      <c r="G13" s="12">
+        <v>-18.6</v>
+      </c>
+      <c r="H13" s="12">
+        <v>2</v>
+      </c>
+      <c r="I13" s="12">
+        <v>5.4</v>
+      </c>
+      <c r="J13" s="15">
+        <v>2.7</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>38</v>
-      </c>
-      <c r="F13" s="13">
-        <v>-13.2</v>
-      </c>
-      <c r="G13" s="13">
-        <v>-18.6</v>
-      </c>
-      <c r="H13" s="13">
-        <v>2</v>
-      </c>
-      <c r="I13" s="13">
-        <v>5.4</v>
-      </c>
-      <c r="J13" s="8">
-        <v>2.7</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>42</v>
       </c>
       <c r="F14" s="16">
         <v>-18.6</v>
@@ -1281,28 +1277,28 @@
       <c r="I14" s="16">
         <v>9.5</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="8">
         <v>6.33</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>45</v>
       </c>
       <c r="F15" s="19">
         <v>-28.1</v>
@@ -1316,28 +1312,28 @@
       <c r="I15" s="19">
         <v>7.1</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="8">
         <v>14.2</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="24" t="s">
         <v>48</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>49</v>
       </c>
       <c r="F16" s="22">
         <v>-35.2</v>
@@ -1351,28 +1347,28 @@
       <c r="I16" s="22">
         <v>3.1</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="8">
         <v>12.4</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>51</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>52</v>
       </c>
       <c r="F17" s="25">
         <v>-38.3</v>
@@ -1386,51 +1382,51 @@
       <c r="I17" s="25">
         <v>5</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="8">
         <v>10</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>55</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>56</v>
       </c>
       <c r="F18" s="28">
         <v>-43.3</v>
       </c>
       <c r="G18" s="28">
-        <v>-49.5</v>
+        <v>-49.53</v>
       </c>
       <c r="H18" s="28">
         <v>1.77</v>
       </c>
       <c r="I18" s="28">
-        <v>6.2</v>
-      </c>
-      <c r="J18" s="8">
-        <v>3.51</v>
+        <v>6.23</v>
+      </c>
+      <c r="J18" s="15">
+        <v>3.53</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1536,31 +1532,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1577,19 +1573,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="G2" s="5">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="I2" s="8">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1606,7 +1602,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-1.2</v>
+        <v>-3.8</v>
       </c>
       <c r="F3" s="9">
         <v>-13.2</v>
@@ -1615,38 +1611,38 @@
         <v>0.5</v>
       </c>
       <c r="H3" s="9">
-        <v>12</v>
-      </c>
-      <c r="I3" s="12">
-        <v>24</v>
+        <v>9.4</v>
+      </c>
+      <c r="I3" s="8">
+        <v>18.8</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="C4" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-13.2</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-18.6</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>2</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>5.4</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="15">
         <v>2.7</v>
       </c>
     </row>
@@ -1658,7 +1654,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1675,7 +1671,7 @@
       <c r="H5" s="16">
         <v>9.5</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="8">
         <v>6.33</v>
       </c>
     </row>
@@ -1687,7 +1683,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1704,7 +1700,7 @@
       <c r="H6" s="19">
         <v>7.1</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="8">
         <v>14.2</v>
       </c>
     </row>
@@ -1716,7 +1712,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1733,7 +1729,7 @@
       <c r="H7" s="22">
         <v>3.1</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="8">
         <v>12.4</v>
       </c>
     </row>
@@ -1745,7 +1741,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1762,7 +1758,7 @@
       <c r="H8" s="25">
         <v>5</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="8">
         <v>10</v>
       </c>
     </row>
@@ -1774,7 +1770,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1783,45 +1779,45 @@
         <v>-43.3</v>
       </c>
       <c r="F9" s="28">
-        <v>-49.5</v>
+        <v>-49.53</v>
       </c>
       <c r="G9" s="28">
         <v>1.77</v>
       </c>
       <c r="H9" s="28">
-        <v>6.2</v>
-      </c>
-      <c r="I9" s="8">
-        <v>3.51</v>
+        <v>6.23</v>
+      </c>
+      <c r="I9" s="15">
+        <v>3.53</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>-49.5</v>
+        <v>-49.53</v>
       </c>
       <c r="G10" s="33">
-        <v>7.35</v>
+        <v>7.52</v>
       </c>
       <c r="H10" s="33">
-        <v>49.5</v>
+        <v>49.53</v>
       </c>
       <c r="I10" s="33">
-        <v>6.73</v>
+        <v>6.59</v>
       </c>
     </row>
   </sheetData>
